--- a/scenarios/S03_sap_fi_consolidation/deliverables/대사현황_키매핑_시트.xlsx
+++ b/scenarios/S03_sap_fi_consolidation/deliverables/대사현황_키매핑_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대사현황" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="키매핑" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개선과제" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -896,4 +897,372 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20260725-fi-internal-trade-key-mapping</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:35:16.182+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>재무 최부장</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S03:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>내부거래대사 키 생성·수정·조회·유효기간·상태·이력 관리와 기존 결산 호환성을 포함한 기능·데이터·화면 설계 변경 및 테스트 시나리오 추가를 승인한다. 권한·감사통제·이력 재현성·마이그레이션·운영 성능 기준은 후속 관리한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>내부거래대사 키 매핑을 표준화하고 결산리포트의 대사결과 조회·확인 효율화를 위한 기능·데이터·화면 설계 변경 및 테스트 시나리오를 추가한다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FI 연결결산 기능정의서; 데이터 모델 및 인터페이스 명세; 결산리포트 화면/조회 설계서; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/cca3744ec0b89d2ecc16ca6938176c44cbb0dd3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20260725-fi-internal-trade-key-mapping-approval-execution-confirmation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:52:36.977+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>재무 최부장</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S03:B00001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7개 영향 산출물의 변경 및 DOCX·XLSX·PPTX 문서엔진 갱신 결과를 승인·기록한다. 적용 범위·기준 시점·권한·감사통제·인터페이스 계약·성능·마이그레이션·롤백 기준은 후속 확정 및 검증 증적 확보를 조건으로 추적한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FI 연결결산 내부거래대사 키를 표준 매핑 구조로 통합하고 결산리포트 조회·필터·정렬·drill-down 및 이력·호환성·재현성·예외·통제·마이그레이션 기준을 7개 영향 산출물에 동기화한다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FI 연결결산 기능정의서; 데이터 모델 및 인터페이스 명세; 결산리포트 화면/조회 설계서; 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/5ed05cd82fe9a999487a096c8bfeaa3315960341</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260725-fi-internal-trade-key-mapping-execution-result</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:48:48.174+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>재무 최부장</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S03:B00010</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7개 영향 산출물의 변경 및 DOCX·XLSX·PPTX 문서엔진 갱신 결과를 승인·기록하며, 권한·감사·재현성·성능·마이그레이션·롤백 기준은 후속 확정 사항으로 추적한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FI 연결결산 내부거래대사 표준 키 매핑과 결산리포트 효율화 요구를 기능·데이터·화면·테스트 산출물에 반영하며 권한·성능·마이그레이션 기준은 후속 확정이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FI 연결결산 기능정의서; 데이터 모델 및 인터페이스 명세; 결산리포트 화면/조회 설계서; 테스트 시나리오; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/94e4541cbfbb3d8754a102098f1d4a7f470c44f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20260725-fi-internal-trade-key-mapping-deliverable-sync</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:45:28.814+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>재무 최부장</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S03:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>승인 페이로드에 따라 7개 영향 산출물의 변경 및 문서엔진 갱신을 승인·기록하며, 적용 범위·기준 시점·권한·감사·cross-module 계약·성능·마이그레이션·롤백 기준은 후속 확정 및 회귀 테스트 대상으로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>내부거래대사 키 표준화, 매핑 이력·예외·호환성·재현성 반영, 결산리포트 조회 개선, 테스트 및 통제 기준 갱신</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FI 연결결산 기능정의서; 데이터 모델 및 인터페이스 명세; 결산리포트 화면/조회 설계서; 테스트 시나리오; 요구사항_추적표.xlsx; 산출물_설계서.docx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/f223a9a3020a36c9f198fa2e01e28ee26acadc40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20260725-fi-internal-trade-key-mapping-execution</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:42:04.396+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>재무 최부장</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S03:B01000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7개 영향 산출물의 변경을 승인하고, 문서엔진 갱신·미매핑 검증 대상 19건·후속 미결정사항을 추적한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FI 연결결산 표준 키 매핑 및 결산리포트 개선: 표준 매핑·이력·호환성·조회·검증·권한·마이그레이션 기준 반영</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FI 연결결산 기능정의서; 데이터 모델 및 인터페이스 명세; 결산리포트 화면/조회 설계서; 테스트 시나리오; 요구사항_추적표.xlsx; 산출물_설계서.docx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/1d43d505f5d288c40fadbbb822777d3751925e62</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20260725-fi-internal-trade-key-mapping-approval</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:38:29.715+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>재무 최부장</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S03:B10000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>승인한다. 단, 적용 범위·시점별 재현성·권한통제·cross-module 영향·성능 및 마이그레이션·롤백 기준을 확정하여 추적표와 테스트에 반영한 후 진행한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>분리 관리되는 내부거래대사 키를 표준 매핑 구조로 통합하고, 매핑 이력·예외·호환성 및 결산리포트 조회 개선을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FI 연결결산 기능정의서; 데이터 모델 및 인터페이스 명세; 결산리포트 화면/조회 설계서; 테스트 시나리오; 요구사항 추적표.xlsx; 산출물_설계서.docx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/7e085eee81cbdce9206739f9065fadaa3ae9df29</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>